--- a/backend/documents/templates/obsluga-egzaminu-rec.xlsx
+++ b/backend/documents/templates/obsluga-egzaminu-rec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projekty Programowanie\McMed\backend\documents\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6057209-C5B8-4801-82AD-B28EAA20D338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820A38AD-6393-46C2-81C0-3C4BFC3FEB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="4" xr2:uid="{9C217465-FFEF-4105-8422-37CB5264C214}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="890" activeTab="4" xr2:uid="{9C217465-FFEF-4105-8422-37CB5264C214}"/>
   </bookViews>
   <sheets>
     <sheet name="DANE " sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
   <si>
     <t>dzień</t>
   </si>
@@ -389,6 +389,27 @@
   <si>
     <t>01.10.2023</t>
   </si>
+  <si>
+    <t>{{p_lp}}</t>
+  </si>
+  <si>
+    <t>{{p_first_name}}</t>
+  </si>
+  <si>
+    <t>{{p_cert_number}}</t>
+  </si>
+  <si>
+    <t>{{p_cert_date}}</t>
+  </si>
+  <si>
+    <t>{{p_new_cert_number}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {{p_new_cert_date}}</t>
+  </si>
+  <si>
+    <t>{{p_last_name}}</t>
+  </si>
 </sst>
 </file>
 
@@ -398,7 +419,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$zł-415];[Red]\-#,##0.00\ [$zł-415]"/>
     <numFmt numFmtId="165" formatCode="d\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -500,6 +521,12 @@
     <font>
       <sz val="9"/>
       <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -620,7 +647,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -649,10 +676,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -670,7 +697,7 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -716,92 +743,73 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1184,20 +1192,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O29"/>
-  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="21.4" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="21.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.58203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="26.5" style="2" customWidth="1"/>
     <col min="3" max="4" width="25.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" style="1" customWidth="1"/>
     <col min="6" max="7" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="39.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="39.58203125" style="3" customWidth="1"/>
     <col min="9" max="9" width="30.75" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.75" style="3" customWidth="1"/>
     <col min="11" max="16384" width="10.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1215,7 +1223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -1253,7 +1261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>14</v>
       </c>
@@ -1266,7 +1274,7 @@
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="44" t="s">
         <v>91</v>
       </c>
       <c r="I3" s="15"/>
@@ -1278,7 +1286,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
@@ -1291,7 +1299,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="55" t="s">
+      <c r="H4" s="44" t="s">
         <v>94</v>
       </c>
       <c r="I4" s="18" t="s">
@@ -1308,7 +1316,7 @@
       </c>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
@@ -1321,7 +1329,7 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="44" t="s">
         <v>97</v>
       </c>
       <c r="I5" s="20" t="s">
@@ -1338,7 +1346,7 @@
       </c>
       <c r="O5" s="19"/>
     </row>
-    <row r="6" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>21</v>
       </c>
@@ -1351,7 +1359,7 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="44" t="s">
         <v>100</v>
       </c>
       <c r="I6" s="18" t="s">
@@ -1368,7 +1376,7 @@
       </c>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>23</v>
       </c>
@@ -1381,7 +1389,7 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="13"/>
-      <c r="H7" s="55" t="s">
+      <c r="H7" s="44" t="s">
         <v>103</v>
       </c>
       <c r="I7" s="20" t="s">
@@ -1398,7 +1406,7 @@
       </c>
       <c r="O7" s="19"/>
     </row>
-    <row r="8" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>25</v>
       </c>
@@ -1418,7 +1426,7 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>27</v>
       </c>
@@ -1435,7 +1443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>29</v>
       </c>
@@ -1451,12 +1459,12 @@
       <c r="L10" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="57" t="s">
+      <c r="M10" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="57"/>
-    </row>
-    <row r="11" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N10" s="50"/>
+    </row>
+    <row r="11" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>32</v>
       </c>
@@ -1472,12 +1480,12 @@
       <c r="L11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M11" s="57" t="s">
+      <c r="M11" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="N11" s="57"/>
-    </row>
-    <row r="12" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N11" s="50"/>
+    </row>
+    <row r="12" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
@@ -1493,12 +1501,12 @@
       <c r="L12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="58" t="s">
+      <c r="M12" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="N12" s="58"/>
-    </row>
-    <row r="13" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N12" s="53"/>
+    </row>
+    <row r="13" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
@@ -1512,7 +1520,7 @@
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>38</v>
       </c>
@@ -1526,7 +1534,7 @@
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>39</v>
       </c>
@@ -1540,7 +1548,7 @@
       <c r="I15" s="26"/>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>40</v>
       </c>
@@ -1554,7 +1562,7 @@
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>41</v>
       </c>
@@ -1568,7 +1576,7 @@
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>42</v>
       </c>
@@ -1582,7 +1590,7 @@
       <c r="I18" s="18"/>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>43</v>
       </c>
@@ -1596,7 +1604,7 @@
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>44</v>
       </c>
@@ -1610,7 +1618,7 @@
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>45</v>
       </c>
@@ -1624,7 +1632,7 @@
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>46</v>
       </c>
@@ -1638,7 +1646,7 @@
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>47</v>
       </c>
@@ -1652,7 +1660,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>48</v>
       </c>
@@ -1666,7 +1674,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>49</v>
       </c>
@@ -1680,7 +1688,7 @@
       <c r="I25" s="8"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>50</v>
       </c>
@@ -1694,7 +1702,7 @@
       <c r="I26" s="8"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>51</v>
       </c>
@@ -1708,7 +1716,7 @@
       <c r="I27" s="8"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>52</v>
       </c>
@@ -1722,7 +1730,7 @@
       <c r="I28" s="8"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="21.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>53</v>
       </c>
@@ -1755,10 +1763,10 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.75" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="22.25" customWidth="1"/>
     <col min="4" max="5" width="10.75" customWidth="1"/>
     <col min="6" max="6" width="15.5" customWidth="1"/>
@@ -1767,45 +1775,45 @@
     <col min="9" max="10" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
       <c r="J2" s="31"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="31"/>
       <c r="H3" s="31"/>
       <c r="I3" s="31"/>
       <c r="J3" s="31"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
         <v>55</v>
       </c>
@@ -1814,23 +1822,23 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+    <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="52" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -1852,7 +1860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>2</v>
       </c>
@@ -1874,7 +1882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>3</v>
       </c>
@@ -1896,7 +1904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -1918,7 +1926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>5</v>
       </c>
@@ -1940,7 +1948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>6</v>
       </c>
@@ -1962,7 +1970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>7</v>
       </c>
@@ -1984,7 +1992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -2006,7 +2014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>9</v>
       </c>
@@ -2022,7 +2030,7 @@
       <c r="E15" s="34"/>
       <c r="F15" s="35"/>
     </row>
-    <row r="16" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>10</v>
       </c>
@@ -2038,7 +2046,7 @@
       <c r="E16" s="34"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>11</v>
       </c>
@@ -2054,7 +2062,7 @@
       <c r="E17" s="34"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" s="36" customFormat="1" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>12</v>
       </c>
@@ -2070,7 +2078,7 @@
       <c r="E18" s="34"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" s="36" customFormat="1" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="21" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>13</v>
       </c>
@@ -2086,7 +2094,7 @@
       <c r="E19" s="34"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>14</v>
       </c>
@@ -2102,7 +2110,7 @@
       <c r="E20" s="34"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>15</v>
       </c>
@@ -2118,7 +2126,7 @@
       <c r="E21" s="34"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>16</v>
       </c>
@@ -2136,7 +2144,7 @@
       <c r="E22" s="34"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>17</v>
       </c>
@@ -2154,7 +2162,7 @@
       <c r="E23" s="34"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>18</v>
       </c>
@@ -2172,7 +2180,7 @@
       <c r="E24" s="34"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>19</v>
       </c>
@@ -2190,7 +2198,7 @@
       <c r="E25" s="34"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>20</v>
       </c>
@@ -2208,7 +2216,7 @@
       <c r="E26" s="34"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>21</v>
       </c>
@@ -2224,7 +2232,7 @@
       <c r="E27" s="34"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>22</v>
       </c>
@@ -2240,7 +2248,7 @@
       <c r="E28" s="34"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>23</v>
       </c>
@@ -2256,7 +2264,7 @@
       <c r="E29" s="34"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>24</v>
       </c>
@@ -2272,7 +2280,7 @@
       <c r="E30" s="34"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>25</v>
       </c>
@@ -2288,7 +2296,7 @@
       <c r="E31" s="34"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>26</v>
       </c>
@@ -2304,7 +2312,7 @@
       <c r="E32" s="34"/>
       <c r="F32" s="5"/>
     </row>
-    <row r="33" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="20.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>27</v>
       </c>
@@ -2320,19 +2328,19 @@
       <c r="E33" s="34"/>
       <c r="F33" s="5"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D34" s="60" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D34" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2362,54 +2370,54 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
-    <col min="2" max="2" width="20.125" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.08203125" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
     <col min="4" max="4" width="10.75" style="2" customWidth="1"/>
     <col min="5" max="10" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
       <c r="I1" s="31"/>
       <c r="J1" s="31"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
       <c r="I2" s="31"/>
       <c r="J2" s="31"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
       <c r="I3" s="31"/>
       <c r="J3" s="31"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="G4" t="s">
         <v>55</v>
       </c>
@@ -2418,27 +2426,27 @@
         <v>46261</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+    <row r="6" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="64"/>
-    </row>
-    <row r="7" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H6" s="54"/>
+    </row>
+    <row r="7" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -2453,10 +2461,10 @@
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-    </row>
-    <row r="8" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+    </row>
+    <row r="8" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>2</v>
       </c>
@@ -2471,10 +2479,10 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-    </row>
-    <row r="9" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+    </row>
+    <row r="9" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>3</v>
       </c>
@@ -2489,10 +2497,10 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-    </row>
-    <row r="10" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+    </row>
+    <row r="10" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -2507,10 +2515,10 @@
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-    </row>
-    <row r="11" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+    </row>
+    <row r="11" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>5</v>
       </c>
@@ -2525,10 +2533,10 @@
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-    </row>
-    <row r="12" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+    </row>
+    <row r="12" spans="1:10" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>6</v>
       </c>
@@ -2543,10 +2551,10 @@
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-    </row>
-    <row r="13" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+    </row>
+    <row r="13" spans="1:10" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>7</v>
       </c>
@@ -2561,10 +2569,10 @@
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-    </row>
-    <row r="14" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+    </row>
+    <row r="14" spans="1:10" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>8</v>
       </c>
@@ -2579,10 +2587,10 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-    </row>
-    <row r="15" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+    </row>
+    <row r="15" spans="1:10" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>9</v>
       </c>
@@ -2597,10 +2605,10 @@
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-    </row>
-    <row r="16" spans="1:10" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+    </row>
+    <row r="16" spans="1:10" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>10</v>
       </c>
@@ -2615,10 +2623,10 @@
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="63"/>
-    </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+    </row>
+    <row r="17" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>11</v>
       </c>
@@ -2633,10 +2641,10 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="63"/>
-    </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+    </row>
+    <row r="18" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>12</v>
       </c>
@@ -2651,10 +2659,10 @@
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-    </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+    </row>
+    <row r="19" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>13</v>
       </c>
@@ -2669,10 +2677,10 @@
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-    </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+    </row>
+    <row r="20" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>14</v>
       </c>
@@ -2687,10 +2695,10 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="63"/>
-    </row>
-    <row r="21" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+    </row>
+    <row r="21" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>15</v>
       </c>
@@ -2705,10 +2713,10 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="63"/>
-    </row>
-    <row r="22" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+    </row>
+    <row r="22" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>16</v>
       </c>
@@ -2723,10 +2731,10 @@
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-    </row>
-    <row r="23" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+    </row>
+    <row r="23" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>17</v>
       </c>
@@ -2741,10 +2749,10 @@
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-    </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+    </row>
+    <row r="24" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>18</v>
       </c>
@@ -2759,10 +2767,10 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-    </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+    </row>
+    <row r="25" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>19</v>
       </c>
@@ -2777,10 +2785,10 @@
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-    </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+    </row>
+    <row r="26" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>20</v>
       </c>
@@ -2795,10 +2803,10 @@
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-    </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+    </row>
+    <row r="27" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>21</v>
       </c>
@@ -2813,10 +2821,10 @@
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-    </row>
-    <row r="28" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+    </row>
+    <row r="28" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>22</v>
       </c>
@@ -2831,10 +2839,10 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-    </row>
-    <row r="29" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+    </row>
+    <row r="29" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>23</v>
       </c>
@@ -2849,10 +2857,10 @@
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-    </row>
-    <row r="30" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+    </row>
+    <row r="30" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>24</v>
       </c>
@@ -2867,10 +2875,10 @@
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-    </row>
-    <row r="31" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+    </row>
+    <row r="31" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>25</v>
       </c>
@@ -2885,10 +2893,10 @@
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-    </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+    </row>
+    <row r="32" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>26</v>
       </c>
@@ -2903,10 +2911,10 @@
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-    </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+    </row>
+    <row r="33" spans="1:8" ht="20.149999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>27</v>
       </c>
@@ -2921,35 +2929,35 @@
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="63"/>
-    </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="D34"/>
-      <c r="F34" s="61" t="s">
+      <c r="F34" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B35" s="2"/>
       <c r="D35"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="60" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="60"/>
-      <c r="C48" s="60"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="60"/>
-      <c r="F48" s="60"/>
-      <c r="G48" s="60"/>
-      <c r="H48" s="60"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="55"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -2959,8 +2967,8 @@
       <c r="F49" t="s">
         <v>66</v>
       </c>
-      <c r="G49" s="62"/>
-      <c r="H49" s="62"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -3011,68 +3019,68 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.75" customWidth="1"/>
     <col min="3" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="6" width="16.375" customWidth="1"/>
-    <col min="7" max="7" width="21.375" customWidth="1"/>
+    <col min="4" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" customWidth="1"/>
     <col min="8" max="9" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="31"/>
       <c r="I3" s="31"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F4" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="36" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="45" t="s">
+    <row r="6" spans="1:9" ht="27.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="40" t="s">
+      <c r="C6" s="54"/>
+      <c r="D6" s="38" t="s">
         <v>78</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -3081,274 +3089,274 @@
       <c r="F6" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="52">
+    <row r="7" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="41" t="str">
+      <c r="B7" s="39" t="str">
         <f>'DANE '!B3</f>
         <v>Kamińska-Wierzchowska</v>
       </c>
-      <c r="C7" s="41" t="str">
+      <c r="C7" s="39" t="str">
         <f>'DANE '!C3</f>
         <v>Karolina</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="53"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="52">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="41" t="str">
+      <c r="B8" s="39" t="str">
         <f>'DANE '!B4</f>
         <v>Faber</v>
       </c>
-      <c r="C8" s="41" t="str">
+      <c r="C8" s="39" t="str">
         <f>'DANE '!C4</f>
         <v>Ewelina</v>
       </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="52">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="41" t="str">
+      <c r="B9" s="39" t="str">
         <f>'DANE '!B5</f>
         <v>Łukowska</v>
       </c>
-      <c r="C9" s="41" t="str">
+      <c r="C9" s="39" t="str">
         <f>'DANE '!C5</f>
         <v>Monika</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="53"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="52">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>4</v>
       </c>
-      <c r="B10" s="41" t="str">
+      <c r="B10" s="39" t="str">
         <f>'DANE '!B6</f>
         <v>Niemiro</v>
       </c>
-      <c r="C10" s="41" t="str">
+      <c r="C10" s="39" t="str">
         <f>'DANE '!C6</f>
         <v>Maciej</v>
       </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="53"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="52">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>5</v>
       </c>
-      <c r="B11" s="41" t="str">
+      <c r="B11" s="39" t="str">
         <f>'DANE '!B7</f>
         <v>Kiela</v>
       </c>
-      <c r="C11" s="41" t="str">
+      <c r="C11" s="39" t="str">
         <f>'DANE '!C7</f>
         <v>Kamil</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="53"/>
-    </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="52">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>6</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="39">
         <f>'DANE '!B8</f>
         <v>0</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="39">
         <f>'DANE '!C8</f>
         <v>0</v>
       </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="53"/>
-    </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="52">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>7</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="39">
         <f>'DANE '!B9</f>
         <v>0</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="39">
         <f>'DANE '!C9</f>
         <v>0</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="53"/>
-    </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="52">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>8</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="39">
         <f>'DANE '!B10</f>
         <v>0</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="39">
         <f>'DANE '!C10</f>
         <v>0</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
-    </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>9</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="39">
         <f>'DANE '!B11</f>
         <v>0</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="39">
         <f>'DANE '!C11</f>
         <v>0</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
       <c r="F15" s="33"/>
-      <c r="G15" s="42"/>
-    </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G15" s="33"/>
+    </row>
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="33">
         <v>10</v>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="39">
         <f>'DANE '!B12</f>
         <v>0</v>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="39">
         <f>'DANE '!C12</f>
         <v>0</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
-      <c r="G16" s="42"/>
-    </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G16" s="33"/>
+    </row>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>11</v>
       </c>
-      <c r="B17" s="41">
+      <c r="B17" s="39">
         <f>'DANE '!B13</f>
         <v>0</v>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="39">
         <f>'DANE '!C13</f>
         <v>0</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
       <c r="F17" s="33"/>
-      <c r="G17" s="42"/>
-    </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G17" s="33"/>
+    </row>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="33">
         <v>12</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="39">
         <f>'DANE '!B14</f>
         <v>0</v>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="39">
         <f>'DANE '!C14</f>
         <v>0</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="33"/>
       <c r="F18" s="33"/>
-      <c r="G18" s="42"/>
-    </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G18" s="33"/>
+    </row>
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>13</v>
       </c>
-      <c r="B19" s="41">
+      <c r="B19" s="39">
         <f>'DANE '!B15</f>
         <v>0</v>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="39">
         <f>'DANE '!C15</f>
         <v>0</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="33"/>
       <c r="F19" s="33"/>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="G19" s="33"/>
+    </row>
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="33">
         <v>14</v>
       </c>
-      <c r="B20" s="41">
+      <c r="B20" s="39">
         <f>'DANE '!B16</f>
         <v>0</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="39">
         <f>'DANE '!C16</f>
         <v>0</v>
       </c>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="43"/>
-    </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>15</v>
       </c>
-      <c r="B21" s="41">
+      <c r="B21" s="39">
         <f>'DANE '!B17</f>
         <v>0</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="39">
         <f>'DANE '!C17</f>
         <v>0</v>
       </c>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-    </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33">
         <v>16</v>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="39">
         <f>'DANE '!B18</f>
         <v>0</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="39">
         <f>'DANE '!C18</f>
         <v>0</v>
       </c>
@@ -3357,15 +3365,15 @@
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>17</v>
       </c>
-      <c r="B23" s="41">
+      <c r="B23" s="39">
         <f>'DANE '!B19</f>
         <v>0</v>
       </c>
-      <c r="C23" s="41">
+      <c r="C23" s="39">
         <f>'DANE '!C19</f>
         <v>0</v>
       </c>
@@ -3374,15 +3382,15 @@
       <c r="F23" s="33"/>
       <c r="G23" s="33"/>
     </row>
-    <row r="24" spans="1:7" ht="25.15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="25.15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="33">
         <v>18</v>
       </c>
-      <c r="B24" s="41">
+      <c r="B24" s="39">
         <f>'DANE '!B20</f>
         <v>0</v>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="39">
         <f>'DANE '!C20</f>
         <v>0</v>
       </c>
@@ -3391,15 +3399,15 @@
       <c r="F24" s="33"/>
       <c r="G24" s="33"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>19</v>
       </c>
-      <c r="B25" s="41">
+      <c r="B25" s="39">
         <f>'DANE '!B21</f>
         <v>0</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="39">
         <f>'DANE '!C21</f>
         <v>0</v>
       </c>
@@ -3408,15 +3416,15 @@
       <c r="F25" s="33"/>
       <c r="G25" s="33"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
         <v>20</v>
       </c>
-      <c r="B26" s="41">
+      <c r="B26" s="39">
         <f>'DANE '!B22</f>
         <v>0</v>
       </c>
-      <c r="C26" s="41">
+      <c r="C26" s="39">
         <f>'DANE '!C22</f>
         <v>0</v>
       </c>
@@ -3425,15 +3433,15 @@
       <c r="F26" s="33"/>
       <c r="G26" s="33"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>21</v>
       </c>
-      <c r="B27" s="41">
+      <c r="B27" s="39">
         <f>'DANE '!B23</f>
         <v>0</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="39">
         <f>'DANE '!C23</f>
         <v>0</v>
       </c>
@@ -3442,15 +3450,15 @@
       <c r="F27" s="33"/>
       <c r="G27" s="33"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
         <v>22</v>
       </c>
-      <c r="B28" s="41">
+      <c r="B28" s="39">
         <f>'DANE '!B24</f>
         <v>0</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="39">
         <f>'DANE '!C24</f>
         <v>0</v>
       </c>
@@ -3459,15 +3467,15 @@
       <c r="F28" s="33"/>
       <c r="G28" s="33"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>23</v>
       </c>
-      <c r="B29" s="41">
+      <c r="B29" s="39">
         <f>'DANE '!B25</f>
         <v>0</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="39">
         <f>'DANE '!C25</f>
         <v>0</v>
       </c>
@@ -3476,15 +3484,15 @@
       <c r="F29" s="33"/>
       <c r="G29" s="33"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>24</v>
       </c>
-      <c r="B30" s="41">
+      <c r="B30" s="39">
         <f>'DANE '!B26</f>
         <v>0</v>
       </c>
-      <c r="C30" s="41">
+      <c r="C30" s="39">
         <f>'DANE '!C26</f>
         <v>0</v>
       </c>
@@ -3493,15 +3501,15 @@
       <c r="F30" s="33"/>
       <c r="G30" s="33"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>25</v>
       </c>
-      <c r="B31" s="41">
+      <c r="B31" s="39">
         <f>'DANE '!B27</f>
         <v>0</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="39">
         <f>'DANE '!C27</f>
         <v>0</v>
       </c>
@@ -3510,15 +3518,15 @@
       <c r="F31" s="33"/>
       <c r="G31" s="33"/>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>26</v>
       </c>
-      <c r="B32" s="41">
+      <c r="B32" s="39">
         <f>'DANE '!B28</f>
         <v>0</v>
       </c>
-      <c r="C32" s="41">
+      <c r="C32" s="39">
         <f>'DANE '!C28</f>
         <v>0</v>
       </c>
@@ -3527,15 +3535,15 @@
       <c r="F32" s="33"/>
       <c r="G32" s="33"/>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>27</v>
       </c>
-      <c r="B33" s="41">
+      <c r="B33" s="39">
         <f>'DANE '!B29</f>
         <v>0</v>
       </c>
-      <c r="C33" s="41">
+      <c r="C33" s="39">
         <f>'DANE '!C29</f>
         <v>0</v>
       </c>
@@ -3544,23 +3552,23 @@
       <c r="F33" s="33"/>
       <c r="G33" s="33"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F34" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="60" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="60"/>
-      <c r="E38" s="60"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="60"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>65</v>
       </c>
@@ -3570,7 +3578,6 @@
       <c r="F39" t="s">
         <v>66</v>
       </c>
-      <c r="G39" s="37"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -3590,241 +3597,147 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.4140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.75" customWidth="1"/>
-    <col min="5" max="5" width="22.25" customWidth="1"/>
-    <col min="6" max="6" width="12.25" customWidth="1"/>
-    <col min="7" max="7" width="4.125" customWidth="1"/>
-    <col min="8" max="10" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.4140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="50"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="31"/>
       <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H4" s="44"/>
-    </row>
-    <row r="6" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-    </row>
-    <row r="7" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="45" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="40"/>
+    </row>
+    <row r="6" spans="1:9" ht="27.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+    </row>
+    <row r="7" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="46" t="s">
+      <c r="C7" s="52"/>
+      <c r="D7" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="67" t="s">
+      <c r="F7" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="67"/>
-      <c r="H7" s="47" t="s">
+      <c r="G7" s="41" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29">
-        <v>1</v>
-      </c>
-      <c r="B8" s="33" t="str">
-        <f>'DANE '!B3</f>
-        <v>Kamińska-Wierzchowska</v>
-      </c>
-      <c r="C8" s="33" t="str">
-        <f>'DANE '!C3</f>
-        <v>Karolina</v>
-      </c>
-      <c r="D8" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="56">
-        <v>45195</v>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>114</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="51" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29">
-        <v>2</v>
-      </c>
-      <c r="B9" s="33" t="str">
-        <f>'DANE '!B4</f>
-        <v>Faber</v>
-      </c>
-      <c r="C9" s="33" t="str">
-        <f>'DANE '!C4</f>
-        <v>Ewelina</v>
-      </c>
-      <c r="D9" s="48" t="str">
-        <f>'DANE '!I4</f>
-        <v>KPP/07/23/01</v>
-      </c>
-      <c r="E9" s="48" t="str">
-        <f>'DANE '!J4</f>
-        <v>01.10.2023</v>
-      </c>
-      <c r="F9" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="51" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="29">
-        <v>3</v>
-      </c>
-      <c r="B10" s="33" t="str">
-        <f>'DANE '!B5</f>
-        <v>Łukowska</v>
-      </c>
-      <c r="C10" s="33" t="str">
-        <f>'DANE '!C5</f>
-        <v>Monika</v>
-      </c>
-      <c r="D10" s="48" t="str">
-        <f>'DANE '!I5</f>
-        <v>71/2023</v>
-      </c>
-      <c r="E10" s="48" t="str">
-        <f>'DANE '!J5</f>
-        <v>26.09.2023</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="H10" s="51" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29">
-        <v>4</v>
-      </c>
-      <c r="B11" s="33" t="str">
-        <f>'DANE '!B6</f>
-        <v>Niemiro</v>
-      </c>
-      <c r="C11" s="33" t="str">
-        <f>'DANE '!C6</f>
-        <v>Maciej</v>
-      </c>
-      <c r="D11" s="48" t="str">
-        <f>'DANE '!I6</f>
-        <v>KPPE/OSP/14/2023/11/1.</v>
-      </c>
-      <c r="E11" s="48" t="str">
-        <f>'DANE '!J6</f>
-        <v>31.08.2023</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="51" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="29">
-        <v>5</v>
-      </c>
-      <c r="B12" s="33" t="str">
-        <f>'DANE '!B7</f>
-        <v>Kiela</v>
-      </c>
-      <c r="C12" s="33" t="str">
-        <f>'DANE '!C7</f>
-        <v>Kamil</v>
-      </c>
-      <c r="D12" s="48" t="str">
-        <f>'DANE '!I7</f>
-        <v>KPP/R/06/23/04</v>
-      </c>
-      <c r="E12" s="48" t="str">
-        <f>'DANE '!J7</f>
-        <v>27.08.2023</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="51" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="29"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="29"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="29"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="29">
         <v>6</v>
       </c>
@@ -3836,25 +3749,22 @@
         <f>'DANE '!C8</f>
         <v>0</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="42">
         <f>'DANE '!I8</f>
         <v>0</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="42">
         <f>'DANE '!J8</f>
         <v>0</v>
       </c>
-      <c r="F13" s="49" t="s">
+      <c r="F13" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="51" t="s">
+      <c r="G13" s="14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="29">
         <v>7</v>
       </c>
@@ -3866,25 +3776,22 @@
         <f>'DANE '!C9</f>
         <v>0</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="42">
         <f>'DANE '!I9</f>
         <v>0</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="42">
         <f>'DANE '!J9</f>
         <v>0</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="51" t="s">
+      <c r="G14" s="14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="29">
         <v>8</v>
       </c>
@@ -3896,25 +3803,22 @@
         <f>'DANE '!C10</f>
         <v>0</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="42">
         <f>'DANE '!I10</f>
         <v>0</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="42">
         <f>'DANE '!J10</f>
         <v>0</v>
       </c>
-      <c r="F15" s="49" t="s">
+      <c r="F15" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="51" t="s">
+      <c r="G15" s="14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="36" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="29">
         <v>9</v>
       </c>
@@ -3926,25 +3830,22 @@
         <f>'DANE '!C11</f>
         <v>0</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="42">
         <f>'DANE '!I11</f>
         <v>0</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="42">
         <f>'DANE '!J11</f>
         <v>0</v>
       </c>
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="51" t="s">
+      <c r="G16" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="29">
         <v>10</v>
       </c>
@@ -3956,25 +3857,22 @@
         <f>'DANE '!C12</f>
         <v>0</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="42">
         <f>'DANE '!I12</f>
         <v>0</v>
       </c>
-      <c r="E17" s="48">
+      <c r="E17" s="42">
         <f>'DANE '!J12</f>
         <v>0</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="51" t="s">
+      <c r="G17" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="29">
         <v>11</v>
       </c>
@@ -3986,25 +3884,22 @@
         <f>'DANE '!C13</f>
         <v>0</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="42">
         <f>'DANE '!I13</f>
         <v>0</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="42">
         <f>'DANE '!J13</f>
         <v>0</v>
       </c>
-      <c r="F18" s="49" t="s">
+      <c r="F18" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="51" t="s">
+      <c r="G18" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="29">
         <v>13</v>
       </c>
@@ -4016,25 +3911,22 @@
         <f>'DANE '!C14</f>
         <v>0</v>
       </c>
-      <c r="D19" s="48">
+      <c r="D19" s="42">
         <f>'DANE '!I14</f>
         <v>0</v>
       </c>
-      <c r="E19" s="48">
+      <c r="E19" s="42">
         <f>'DANE '!J14</f>
         <v>0</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19" s="51" t="s">
+      <c r="G19" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="29">
         <v>14</v>
       </c>
@@ -4046,25 +3938,22 @@
         <f>'DANE '!C15</f>
         <v>0</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="42">
         <f>'DANE '!I15</f>
         <v>0</v>
       </c>
-      <c r="E20" s="48">
+      <c r="E20" s="42">
         <f>'DANE '!J15</f>
         <v>0</v>
       </c>
-      <c r="F20" s="49" t="s">
+      <c r="F20" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G20" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" s="51" t="s">
+      <c r="G20" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="29">
         <v>15</v>
       </c>
@@ -4076,25 +3965,22 @@
         <f>'DANE '!C16</f>
         <v>0</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="42">
         <f>'DANE '!I16</f>
         <v>0</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="42">
         <f>'DANE '!J16</f>
         <v>0</v>
       </c>
-      <c r="F21" s="49" t="s">
+      <c r="F21" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="51" t="s">
+      <c r="G21" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="29">
         <v>16</v>
       </c>
@@ -4106,25 +3992,22 @@
         <f>'DANE '!C17</f>
         <v>0</v>
       </c>
-      <c r="D22" s="48">
+      <c r="D22" s="42">
         <f>'DANE '!I17</f>
         <v>0</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="42">
         <f>'DANE '!J17</f>
         <v>0</v>
       </c>
-      <c r="F22" s="49" t="s">
+      <c r="F22" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G22" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="51" t="s">
+      <c r="G22" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="29">
         <v>17</v>
       </c>
@@ -4136,25 +4019,22 @@
         <f>'DANE '!C18</f>
         <v>0</v>
       </c>
-      <c r="D23" s="48">
+      <c r="D23" s="42">
         <f>'DANE '!I18</f>
         <v>0</v>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="42">
         <f>'DANE '!J18</f>
         <v>0</v>
       </c>
-      <c r="F23" s="49" t="s">
+      <c r="F23" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="51" t="s">
+      <c r="G23" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="29">
         <v>18</v>
       </c>
@@ -4166,25 +4046,22 @@
         <f>'DANE '!C19</f>
         <v>0</v>
       </c>
-      <c r="D24" s="48">
+      <c r="D24" s="42">
         <f>'DANE '!I19</f>
         <v>0</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="42">
         <f>'DANE '!J19</f>
         <v>0</v>
       </c>
-      <c r="F24" s="49" t="s">
+      <c r="F24" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G24" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="51" t="s">
+      <c r="G24" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29">
         <v>19</v>
       </c>
@@ -4196,25 +4073,22 @@
         <f>'DANE '!C20</f>
         <v>0</v>
       </c>
-      <c r="D25" s="48">
+      <c r="D25" s="42">
         <f>'DANE '!I20</f>
         <v>0</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="42">
         <f>'DANE '!J20</f>
         <v>0</v>
       </c>
-      <c r="F25" s="49" t="s">
+      <c r="F25" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="51" t="s">
+      <c r="G25" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="29">
         <v>20</v>
       </c>
@@ -4226,25 +4100,22 @@
         <f>'DANE '!C21</f>
         <v>0</v>
       </c>
-      <c r="D26" s="48">
+      <c r="D26" s="42">
         <f>'DANE '!I21</f>
         <v>0</v>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="42">
         <f>'DANE '!J21</f>
         <v>0</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G26" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26" s="51" t="s">
+      <c r="G26" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="29">
         <v>21</v>
       </c>
@@ -4256,25 +4127,22 @@
         <f>'DANE '!C22</f>
         <v>0</v>
       </c>
-      <c r="D27" s="48">
+      <c r="D27" s="42">
         <f>'DANE '!I22</f>
         <v>0</v>
       </c>
-      <c r="E27" s="48">
+      <c r="E27" s="42">
         <f>'DANE '!J22</f>
         <v>0</v>
       </c>
-      <c r="F27" s="49" t="s">
+      <c r="F27" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27" s="51" t="s">
+      <c r="G27" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
         <v>22</v>
       </c>
@@ -4286,25 +4154,22 @@
         <f>'DANE '!C23</f>
         <v>0</v>
       </c>
-      <c r="D28" s="48">
+      <c r="D28" s="42">
         <f>'DANE '!I23</f>
         <v>0</v>
       </c>
-      <c r="E28" s="48">
+      <c r="E28" s="42">
         <f>'DANE '!J23</f>
         <v>0</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G28" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="H28" s="51" t="s">
+      <c r="G28" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="29">
         <v>23</v>
       </c>
@@ -4316,25 +4181,22 @@
         <f>'DANE '!C24</f>
         <v>0</v>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="42">
         <f>'DANE '!I24</f>
         <v>0</v>
       </c>
-      <c r="E29" s="48">
+      <c r="E29" s="42">
         <f>'DANE '!J24</f>
         <v>0</v>
       </c>
-      <c r="F29" s="49" t="s">
+      <c r="F29" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29" s="51" t="s">
+      <c r="G29" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="29">
         <v>24</v>
       </c>
@@ -4346,25 +4208,22 @@
         <f>'DANE '!C25</f>
         <v>0</v>
       </c>
-      <c r="D30" s="48">
+      <c r="D30" s="42">
         <f>'DANE '!I25</f>
         <v>0</v>
       </c>
-      <c r="E30" s="48">
+      <c r="E30" s="42">
         <f>'DANE '!J25</f>
         <v>0</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="F30" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="51" t="s">
+      <c r="G30" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="29">
         <v>25</v>
       </c>
@@ -4376,25 +4235,22 @@
         <f>'DANE '!C26</f>
         <v>0</v>
       </c>
-      <c r="D31" s="48">
+      <c r="D31" s="42">
         <f>'DANE '!I26</f>
         <v>0</v>
       </c>
-      <c r="E31" s="48">
+      <c r="E31" s="42">
         <f>'DANE '!J26</f>
         <v>0</v>
       </c>
-      <c r="F31" s="49" t="s">
+      <c r="F31" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G31" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="51" t="s">
+      <c r="G31" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="29">
         <v>26</v>
       </c>
@@ -4406,25 +4262,22 @@
         <f>'DANE '!C27</f>
         <v>0</v>
       </c>
-      <c r="D32" s="48">
+      <c r="D32" s="42">
         <f>'DANE '!I27</f>
         <v>0</v>
       </c>
-      <c r="E32" s="48">
+      <c r="E32" s="42">
         <f>'DANE '!J27</f>
         <v>0</v>
       </c>
-      <c r="F32" s="49" t="s">
+      <c r="F32" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G32" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="H32" s="51" t="s">
+      <c r="G32" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="29">
         <v>27</v>
       </c>
@@ -4436,32 +4289,29 @@
         <f>'DANE '!C28</f>
         <v>0</v>
       </c>
-      <c r="D33" s="48">
+      <c r="D33" s="42">
         <f>'DANE '!I28</f>
         <v>0</v>
       </c>
-      <c r="E33" s="48">
+      <c r="E33" s="42">
         <f>'DANE '!J28</f>
         <v>0</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G33" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="H33" s="51" t="s">
+      <c r="G33" s="14" t="s">
         <v>76</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="4">
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="A6:H6"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G3"/>
+    <mergeCell ref="A6:G6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
